--- a/out/LSTM-mamba2_repeat_4_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>-6.664684045733884e-05</v>
+        <v>-9.315708769287449e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07656441897983193</v>
+        <v>-0.1070196012911481</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.07668934425075201</v>
+        <v>-0.107195290178011</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.209555963578679</v>
+        <v>0.2967655539730406</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3428249380303537</v>
+        <v>0.4869056184988809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01493078182119978</v>
+        <v>0.0211444468266281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1627944606620776</v>
+        <v>0.2319529869918532</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02618363240146728</v>
+        <v>0.03708028369412986</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2002258876982583</v>
+        <v>0.2849619779636297</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03180970931880176</v>
+        <v>0.04504816554161525</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.237659806696597</v>
+        <v>0.3379744971440681</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.008416269525824298</v>
+        <v>0.0119208732929875</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2226431064235747</v>
+        <v>0.3167105636086252</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004673725894910916</v>
+        <v>0.00662071862793783</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2235676409372315</v>
+        <v>0.3180218968864733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009824591766019384</v>
+        <v>0.01391396089809551</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2385478256150614</v>
+        <v>0.3392374891218566</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003855902714314617</v>
+        <v>0.005462997413779955</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2364285338044378</v>
+        <v>0.336238264329596</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002744546605466307</v>
+        <v>0.003889903535221407</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2380606300654393</v>
+        <v>0.3385515840686287</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001077239285479939</v>
+        <v>0.001528059163496676</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2374680546309757</v>
+        <v>0.337714767537842</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006100238536367782</v>
+        <v>0.0008643570261933406</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.237608873741017</v>
+        <v>0.3379160715260736</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002286994769056626</v>
+        <v>0.0003261721230522456</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2374569323396203</v>
+        <v>0.3377029962801158</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001050960443416172</v>
+        <v>0.0001502354225216803</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.237437083511764</v>
+        <v>0.3376769859358545</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.536626471769872e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.237402627642018</v>
+        <v>0.3376301586008151</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2373810722046467</v>
+        <v>0.3376016502520689</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.238290199080266e-07</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2373760632689423</v>
+        <v>0.3375966368485123</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2373715362668946</v>
+        <v>0.337592291222703</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2373678194364149</v>
+        <v>0.3375889408679101</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2373625236064107</v>
+        <v>0.3375835715409224</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.237356861609407</v>
+        <v>0.3375775788074921</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2373566778669478</v>
+        <v>0.3375722110189137</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2373567146154395</v>
+        <v>0.3375722477674054</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2373568248609151</v>
+        <v>0.3375723580128809</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2373568983578987</v>
+        <v>0.3375724315098645</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2373570821003579</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2373586255370143</v>
+        <v>0.3375741586889802</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2373600954766874</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2373613449254094</v>
+        <v>0.3375768780773752</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2373627046196067</v>
+        <v>0.3375782377715725</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2373604997100975</v>
+        <v>0.3375760328620633</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2373600954766874</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2373598014887527</v>
+        <v>0.3375753346407185</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2373594707523263</v>
+        <v>0.3375750039042921</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2373591767643918</v>
+        <v>0.3375747099163576</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2373588092794735</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2373586990339979</v>
+        <v>0.3375742321859638</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2373586622855063</v>
+        <v>0.3375741954374721</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2373588092794735</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2373583315490798</v>
+        <v>0.3375738647010457</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2373592870098671</v>
+        <v>0.337574820161833</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.237358919524949</v>
+        <v>0.3375744526769149</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.237359360506851</v>
+        <v>0.3375748936588168</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2373587357824899</v>
+        <v>0.3375742689344557</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2373585520400307</v>
+        <v>0.3375740851919966</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2373581478066207</v>
+        <v>0.3375736809585865</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2373573025913087</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.237357265842817</v>
+        <v>0.3375727989947828</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2373574128367843</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2373573393398006</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2373574128367843</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2373574495852762</v>
+        <v>0.337572982737242</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2373573393398006</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2373577803217026</v>
+        <v>0.3375733134736684</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.237357670076227</v>
+        <v>0.3375732032281928</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2373576333277351</v>
+        <v>0.3375731664797009</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2373575598307515</v>
+        <v>0.3375730929827173</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2373575230822598</v>
+        <v>0.3375730562342256</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2373573025913087</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2373572290943251</v>
+        <v>0.3375727622462909</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2373571555973415</v>
+        <v>0.3375726887493073</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2373571923458334</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2373570821003579</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2373571923458334</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2373574863337679</v>
+        <v>0.3375730194857337</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121085</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.986393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121086</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC45" t="n">
-        <v>-6.664684045733884e-05</v>
+        <v>-8.090905526245479e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07656441897983193</v>
+        <v>-0.09294896448004428</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.07663106582028931</v>
+        <v>-0.09302987353530666</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.07668934425075201</v>
+        <v>-0.09310142222967395</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.209555963578679</v>
+        <v>0.2572728104014165</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3428249380303537</v>
+        <v>0.4219381717901374</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01493078182119978</v>
+        <v>0.01833059713888527</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1627944606620776</v>
+        <v>0.2009139351747194</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02618363240146728</v>
+        <v>0.03214562176013905</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2002258876982583</v>
+        <v>0.2468686479526483</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03180970931880176</v>
+        <v>0.03905313407076604</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.237659806696597</v>
+        <v>0.292826603145998</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.008416269525824298</v>
+        <v>0.01033388629858316</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2226431064235747</v>
+        <v>0.2743916386330405</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004673725894910916</v>
+        <v>0.005739123840399922</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2235676409372315</v>
+        <v>0.2755278301301552</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009824591766019384</v>
+        <v>0.01206272368451713</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2385478256150614</v>
+        <v>0.293920040549276</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003855902714314617</v>
+        <v>0.004735142165566942</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2364285338044378</v>
+        <v>0.2913193385316676</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002744546605466307</v>
+        <v>0.003370698059534231</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2380606300654393</v>
+        <v>0.2933241318986342</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001077239285479939</v>
+        <v>0.001324375483669837</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2374680546309757</v>
+        <v>0.2925978312931075</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006100238536367782</v>
+        <v>0.0007487510386676304</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.237608873741017</v>
+        <v>0.2927717256741885</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002286994769056626</v>
+        <v>0.0002827204615170218</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2374569323396203</v>
+        <v>0.2925862703498812</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001050960443416172</v>
+        <v>0.000129317174096773</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.237437083511764</v>
+        <v>0.2925630812829125</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.536626471769872e-05</v>
+        <v>4.424684295559244e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.237402627642018</v>
+        <v>0.2925218511338879</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>9.78655830142907e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2373810722046467</v>
+        <v>0.2924963223915475</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.238290199080266e-07</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2373760632689423</v>
+        <v>0.2924913112219169</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2373715362668946</v>
+        <v>0.2924868928878643</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2373678194364149</v>
+        <v>0.2924833587906123</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2373625236064107</v>
+        <v>0.2924780629606082</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.237356861609407</v>
+        <v>0.2924724009636044</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2373566778669478</v>
+        <v>0.2924722172211453</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2373567146154395</v>
+        <v>0.292472253969637</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2373568248609151</v>
+        <v>0.2924723642151125</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2373568983578987</v>
+        <v>0.2924724377120961</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121086</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2373570821003579</v>
+        <v>0.2924726214545553</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2373586255370143</v>
+        <v>0.2924741648912118</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2373600954766874</v>
+        <v>0.2924756348308848</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2373613449254094</v>
+        <v>0.2924768842796069</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2373627046196067</v>
+        <v>0.2924782439738042</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2373604997100975</v>
+        <v>0.2924760390642949</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121086</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2373600954766874</v>
+        <v>0.2924756348308848</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.2924747896155729</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2373598014887527</v>
+        <v>0.2924753408429502</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2373594707523263</v>
+        <v>0.2924750101065238</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2373591767643918</v>
+        <v>0.2924747161185893</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.2924747896155729</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2373588092794735</v>
+        <v>0.2924743486336709</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2373586990339979</v>
+        <v>0.2924742383881954</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2373586622855063</v>
+        <v>0.2924742016397037</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2373588092794735</v>
+        <v>0.2924743486336709</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2373583315490798</v>
+        <v>0.2924738709032773</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2373592870098671</v>
+        <v>0.2924748263640646</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2373592502613754</v>
+        <v>0.2924747896155729</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.237358919524949</v>
+        <v>0.2924744588791465</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.237359360506851</v>
+        <v>0.2924748998610485</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2373587357824899</v>
+        <v>0.2924742751366873</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2373585520400307</v>
+        <v>0.2924740913942281</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2373581478066207</v>
+        <v>0.2924736871608181</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2373573025913087</v>
+        <v>0.2924728419455062</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.237357265842817</v>
+        <v>0.2924728051970145</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2373574128367843</v>
+        <v>0.2924729521909817</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2373573393398006</v>
+        <v>0.2924728786939981</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2373574128367843</v>
+        <v>0.2924729521909817</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2373574495852762</v>
+        <v>0.2924729889394737</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2373573393398006</v>
+        <v>0.2924728786939981</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2373577803217026</v>
+        <v>0.2924733196759001</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.237357670076227</v>
+        <v>0.2924732094304245</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2373576333277351</v>
+        <v>0.2924731726819326</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2373575598307515</v>
+        <v>0.292473099184949</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2373575230822598</v>
+        <v>0.2924730624364573</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2373573025913087</v>
+        <v>0.2924728419455062</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2373572290943251</v>
+        <v>0.2924727684485225</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768308</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2373571555973415</v>
+        <v>0.2924726949515389</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2373571923458334</v>
+        <v>0.2924727317000309</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2373570821003579</v>
+        <v>0.2924726214545553</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.862243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2373571923458334</v>
+        <v>0.2924727317000309</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.862243845257878</v>
+        <v>-0.6369672081768307</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2373574863337679</v>
+        <v>0.2924730256879653</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2307600528001785</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.07996140420436859</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0203330535441637</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.03343214467167854</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.03820177912712097</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.04316622391343117</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.03675096854567528</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.316383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.02260379493236542</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0178811326622963</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01367509365081787</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.316383792256578</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01505117118358612</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.316383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01006045192480087</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.316383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.009148688986897469</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.005499817430973053</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.004508160054683685</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005574636161327362</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01351968571543694</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.116383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01728404313325882</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.116383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01761383935809135</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.116383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01617219299077988</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.116383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01201283559203148</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.116383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0122716948390007</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.116383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.007818050682544708</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.006399147212505341</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002867113798856735</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.005503267049789429</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.00513814389705658</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.006200574338436127</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.004311088472604752</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.004061408340930939</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.004819203168153763</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4652667921121085</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002178438007831573</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.008871953934431076</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01024405285716057</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00687689334154129</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01136406883597374</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.316383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.005535263568162918</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.316383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.004661224782466888</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.316383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.005216613411903381</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6652667921121086</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0004556328058242798</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0009232647716999054</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.004476062953472137</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.01200646348297596</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.03491208702325821</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.090905526245479e-05</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09294896448004428</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03380469977855682</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001843702048063278</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.002821143716573715</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.005274901166558266</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.316383792256578</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.004159105941653252</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.006058435887098312</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.316383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.002902967855334282</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.316383792256578</v>
+        <v>0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.003343386575579643</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002717418596148491</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00490151159465313</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.005391968414187431</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.004625262692570686</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004559166729450226</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09302987353530666</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01028857938945293</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09310142222967395</v>
+        <v>-0.08882259802308166</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2572728104014165</v>
+        <v>0.2450100850180599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01954573765397072</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4219381717901374</v>
+        <v>0.4016685148271203</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01833059713888527</v>
+        <v>0.01745691711621853</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005182606168091297</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2009139351747194</v>
+        <v>0.191178799990556</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03214562176013905</v>
+        <v>0.03061348468161163</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.006132231093943119</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2468686479526483</v>
+        <v>0.2349432102014082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03905313407076604</v>
+        <v>0.03719176846430827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01575310900807381</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.292826603145998</v>
+        <v>0.2787107170440257</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01033388629858316</v>
+        <v>0.009841275378308329</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01263276115059853</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2743916386330405</v>
+        <v>0.2611541543437242</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005739123840399922</v>
+        <v>0.005465436902612457</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01738136261701584</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2755278301301552</v>
+        <v>0.2622359371537592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01206272368451713</v>
+        <v>0.01148623516005559</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.03712088987231255</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.293920040549276</v>
+        <v>0.2797504684094372</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004735142165566942</v>
+        <v>0.004509882471444446</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.03986004367470741</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2913193385316676</v>
+        <v>0.2772734336275656</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003370698059534231</v>
+        <v>0.00321027909196311</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.05099823698401451</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2933241318986342</v>
+        <v>0.2791822281331267</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001324375483669837</v>
+        <v>0.001260554597324094</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.05425554141402245</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2925978312931075</v>
+        <v>0.2784905558508476</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007487510386676304</v>
+        <v>0.0007132985358264126</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.05952899530529976</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2927717256741885</v>
+        <v>0.27865586087661</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002827204615170218</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.05877925083041191</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2925862703498812</v>
+        <v>0.2784792441804321</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000129317174096773</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.05017689988017082</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2925630812829125</v>
+        <v>0.2784569460431346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.424684295559244e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03992796316742897</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2925218511338879</v>
+        <v>0.278417483246295</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.78655830142907e-06</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0252945888787508</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2924963223915475</v>
+        <v>0.2783929482025178</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01708872243762016</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2924913112219169</v>
+        <v>0.278387937032887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01246062852442265</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2924868928878643</v>
+        <v>0.2783834827390828</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01144927274435759</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2924833587906123</v>
+        <v>0.2783799486418308</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008821545168757439</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2924780629606082</v>
+        <v>0.2783746528118267</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00111403688788414</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2924724009636044</v>
+        <v>0.278368990814823</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.008171975612640381</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2924722172211453</v>
+        <v>0.2783688070723638</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.006744354963302612</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.292472253969637</v>
+        <v>0.2783688438208555</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.007489896379411221</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2924723642151125</v>
+        <v>0.2783689540663311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.006294104270637035</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.316383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2924724377120961</v>
+        <v>0.2783690275633147</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.008820551447570324</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6652667921121086</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2924726214545553</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02087677456438541</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2924741648912118</v>
+        <v>0.2783707547424303</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.03533175960183144</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2924756348308848</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.05269838869571686</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2924768842796069</v>
+        <v>0.2783734741308254</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0835595577955246</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2924782439738042</v>
+        <v>0.2783748338250227</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.07174727320671082</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2924760390642949</v>
+        <v>0.2783726289155134</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02140424773097038</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6652667921121086</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2924756348308848</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02438570559024811</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.01414979196763891</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2924747896155729</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.07393352687358856</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2924753408429502</v>
+        <v>0.2783719306941687</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.1130997240543365</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2924750101065238</v>
+        <v>0.2783715999577422</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.1276047378778458</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2924747161185893</v>
+        <v>0.2783713059698078</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.1361308693885803</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2924747896155729</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.1311204880475998</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2924743486336709</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.1228479593992233</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2924742383881954</v>
+        <v>0.2783708282394139</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.1065676957368851</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2924742016397037</v>
+        <v>0.2783707914909222</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.09841936826705933</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2924743486336709</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0821252316236496</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2924738709032773</v>
+        <v>0.2783704607544958</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.05692749097943306</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2924748263640646</v>
+        <v>0.2783714162152831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.07486911118030548</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2924747896155729</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.09038648009300232</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2924744588791465</v>
+        <v>0.278371048730365</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.09870974719524384</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2924748998610485</v>
+        <v>0.2783714897122669</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.1024737060070038</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2924742751366873</v>
+        <v>0.2783708649879058</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.09756109118461609</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2924740913942281</v>
+        <v>0.2783706812454467</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.09384468197822571</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8369672081768308</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2924736871608181</v>
+        <v>0.2783702770120366</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.07576827704906464</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2924728419455062</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.05596272274851799</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2924728051970145</v>
+        <v>0.278369395048233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.05241858959197998</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2924729521909817</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.04045596346259117</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2924728786939981</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.03670785203576088</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2924729521909817</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.03098191693425179</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2924729889394737</v>
+        <v>0.2783695787906921</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02659647725522518</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2924728786939981</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.03001894056797028</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2924733196759001</v>
+        <v>0.2783699095271185</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02900786884129047</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2924732094304245</v>
+        <v>0.278369799281643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02704179473221302</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2924731726819326</v>
+        <v>0.2783697625331511</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02664109505712986</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.292473099184949</v>
+        <v>0.2783696890361674</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02165227383375168</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2924730624364573</v>
+        <v>0.2783696522876757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01403946522623301</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2924728419455062</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00669392105191946</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2924727684485225</v>
+        <v>0.2783693582997411</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00350419245660305</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8369672081768308</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2924726949515389</v>
+        <v>0.2783692848027574</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001006095670163631</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2924727317000309</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>9.093526750802994e-05</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2924726214545553</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004346205852925777</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.1199999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2924727317000309</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01243280805647373</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6369672081768307</v>
+        <v>-0.02000000000000046</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2924730256879653</v>
+        <v>0.2783696155391838</v>
       </c>
     </row>
   </sheetData>
